--- a/SNAP_Bivariate_Classification_Dataset.xlsx
+++ b/SNAP_Bivariate_Classification_Dataset.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nowsh\Downloads\Research\Fall 2025\food_insecurity_dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8E68379-A32C-44C0-A34B-344868896114}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{518BC16B-84BB-4E5C-82B1-DDBCD822611F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="1" xr2:uid="{85984DDD-8E03-4E71-BB7D-ACE5956AC118}"/>
   </bookViews>
@@ -19,7 +19,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Agency_Data!$A$1:$J$218</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Sheet3!$A$1:$S$533</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Sheet3!$A$1:$T$533</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10658" uniqueCount="1581">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10659" uniqueCount="1582">
   <si>
     <t>fips</t>
   </si>
@@ -4789,6 +4789,9 @@
   </si>
   <si>
     <t>Average Increase in Visit</t>
+  </si>
+  <si>
+    <t>Excluded from Service Region</t>
   </si>
 </sst>
 </file>
@@ -27158,7 +27161,8 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A7F1BB22-D0D6-4DBD-A1C6-B20ABF137412}">
-  <dimension ref="A1:S533"/>
+  <sheetPr filterMode="1"/>
+  <dimension ref="A1:T533"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="10.81640625" bestFit="1" customWidth="1"/>
@@ -27168,7 +27172,7 @@
     <col min="17" max="17" width="34.36328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="52.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:20" ht="52.5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -27226,8 +27230,11 @@
       <c r="S1" s="1" t="s">
         <v>1575</v>
       </c>
-    </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T1" s="1" t="s">
+        <v>1581</v>
+      </c>
+    </row>
+    <row r="2" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A2" s="2">
         <v>37001</v>
       </c>
@@ -27285,8 +27292,11 @@
       <c r="S2" t="s">
         <v>1576</v>
       </c>
-    </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A3" s="2">
         <v>37001</v>
       </c>
@@ -27344,8 +27354,11 @@
       <c r="S3" t="s">
         <v>1576</v>
       </c>
-    </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A4" s="2">
         <v>37001</v>
       </c>
@@ -27403,8 +27416,11 @@
       <c r="S4" t="s">
         <v>1576</v>
       </c>
-    </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A5" s="2">
         <v>37001</v>
       </c>
@@ -27462,8 +27478,11 @@
       <c r="S5" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A6" s="2">
         <v>37001</v>
       </c>
@@ -27521,8 +27540,11 @@
       <c r="S6" t="s">
         <v>1576</v>
       </c>
-    </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A7" s="2">
         <v>37001</v>
       </c>
@@ -27580,8 +27602,11 @@
       <c r="S7" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A8" s="2">
         <v>37001</v>
       </c>
@@ -27639,8 +27664,11 @@
       <c r="S8" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A9" s="2">
         <v>37001</v>
       </c>
@@ -27698,8 +27726,11 @@
       <c r="S9" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A10" s="2">
         <v>37001</v>
       </c>
@@ -27757,8 +27788,11 @@
       <c r="S10" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A11" s="2">
         <v>37001</v>
       </c>
@@ -27816,8 +27850,11 @@
       <c r="S11" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A12" s="2">
         <v>37001</v>
       </c>
@@ -27875,8 +27912,11 @@
       <c r="S12" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A13" s="2">
         <v>37001</v>
       </c>
@@ -27934,8 +27974,11 @@
       <c r="S13" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A14" s="2">
         <v>37001</v>
       </c>
@@ -27993,8 +28036,11 @@
       <c r="S14" t="s">
         <v>1576</v>
       </c>
-    </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A15" s="2">
         <v>37001</v>
       </c>
@@ -28052,8 +28098,11 @@
       <c r="S15" t="s">
         <v>1576</v>
       </c>
-    </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A16" s="2">
         <v>37001</v>
       </c>
@@ -28111,8 +28160,11 @@
       <c r="S16" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="17" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A17" s="2">
         <v>37001</v>
       </c>
@@ -28170,8 +28222,11 @@
       <c r="S17" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="18" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A18" s="2">
         <v>37001</v>
       </c>
@@ -28229,8 +28284,11 @@
       <c r="S18" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="19" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A19" s="2">
         <v>37001</v>
       </c>
@@ -28288,8 +28346,11 @@
       <c r="S19" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="20" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A20" s="2">
         <v>37001</v>
       </c>
@@ -28347,8 +28408,11 @@
       <c r="S20" t="s">
         <v>1576</v>
       </c>
-    </row>
-    <row r="21" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A21" s="2">
         <v>37001</v>
       </c>
@@ -28406,8 +28470,11 @@
       <c r="S21" t="s">
         <v>1576</v>
       </c>
-    </row>
-    <row r="22" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A22" s="2">
         <v>37001</v>
       </c>
@@ -28465,8 +28532,11 @@
       <c r="S22" t="s">
         <v>1576</v>
       </c>
-    </row>
-    <row r="23" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A23" s="2">
         <v>37001</v>
       </c>
@@ -28524,8 +28594,11 @@
       <c r="S23" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="24" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A24" s="2">
         <v>37001</v>
       </c>
@@ -28583,8 +28656,11 @@
       <c r="S24" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="25" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A25" s="2">
         <v>37001</v>
       </c>
@@ -28642,8 +28718,11 @@
       <c r="S25" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="26" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A26" s="2">
         <v>37001</v>
       </c>
@@ -28701,8 +28780,11 @@
       <c r="S26" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="27" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A27" s="2">
         <v>37001</v>
       </c>
@@ -28760,8 +28842,11 @@
       <c r="S27" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="28" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A28" s="2">
         <v>37001</v>
       </c>
@@ -28819,8 +28904,11 @@
       <c r="S28" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="29" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A29" s="2">
         <v>37001</v>
       </c>
@@ -28878,8 +28966,11 @@
       <c r="S29" t="s">
         <v>1576</v>
       </c>
-    </row>
-    <row r="30" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A30" s="2">
         <v>37001</v>
       </c>
@@ -28937,8 +29028,11 @@
       <c r="S30" t="s">
         <v>1576</v>
       </c>
-    </row>
-    <row r="31" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A31" s="2">
         <v>37001</v>
       </c>
@@ -28996,8 +29090,11 @@
       <c r="S31" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="32" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A32" s="2">
         <v>37001</v>
       </c>
@@ -29055,8 +29152,11 @@
       <c r="S32" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="33" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A33" s="2">
         <v>37001</v>
       </c>
@@ -29114,8 +29214,11 @@
       <c r="S33" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="34" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A34" s="2">
         <v>37001</v>
       </c>
@@ -29173,8 +29276,11 @@
       <c r="S34" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="35" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A35" s="2">
         <v>37001</v>
       </c>
@@ -29232,8 +29338,11 @@
       <c r="S35" t="s">
         <v>1576</v>
       </c>
-    </row>
-    <row r="36" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A36" s="2">
         <v>37001</v>
       </c>
@@ -29291,8 +29400,11 @@
       <c r="S36" t="s">
         <v>1576</v>
       </c>
-    </row>
-    <row r="37" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A37" s="2">
         <v>37001</v>
       </c>
@@ -29350,8 +29462,11 @@
       <c r="S37" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="38" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A38" s="2">
         <v>37001</v>
       </c>
@@ -29409,8 +29524,11 @@
       <c r="S38" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="39" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A39" s="2">
         <v>37003</v>
       </c>
@@ -29468,8 +29586,11 @@
       <c r="S39" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="40" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A40" s="2">
         <v>37003</v>
       </c>
@@ -29527,8 +29648,11 @@
       <c r="S40" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="41" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A41" s="2">
         <v>37003</v>
       </c>
@@ -29586,8 +29710,11 @@
       <c r="S41" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="42" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A42" s="2">
         <v>37003</v>
       </c>
@@ -29645,8 +29772,11 @@
       <c r="S42" t="s">
         <v>1576</v>
       </c>
-    </row>
-    <row r="43" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A43" s="2">
         <v>37003</v>
       </c>
@@ -29704,8 +29834,11 @@
       <c r="S43" t="s">
         <v>1576</v>
       </c>
-    </row>
-    <row r="44" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A44" s="2">
         <v>37003</v>
       </c>
@@ -29763,8 +29896,11 @@
       <c r="S44" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="45" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A45" s="2">
         <v>37003</v>
       </c>
@@ -29822,8 +29958,11 @@
       <c r="S45" t="s">
         <v>1576</v>
       </c>
-    </row>
-    <row r="46" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A46" s="2">
         <v>37005</v>
       </c>
@@ -29881,8 +30020,11 @@
       <c r="S46" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="47" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A47" s="2">
         <v>37005</v>
       </c>
@@ -29940,8 +30082,11 @@
       <c r="S47" t="s">
         <v>1576</v>
       </c>
-    </row>
-    <row r="48" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A48" s="2">
         <v>37005</v>
       </c>
@@ -29999,8 +30144,11 @@
       <c r="S48" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="49" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A49" s="2">
         <v>37009</v>
       </c>
@@ -30058,8 +30206,11 @@
       <c r="S49" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="50" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A50" s="2">
         <v>37009</v>
       </c>
@@ -30117,8 +30268,11 @@
       <c r="S50" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="51" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A51" s="2">
         <v>37009</v>
       </c>
@@ -30176,8 +30330,11 @@
       <c r="S51" t="s">
         <v>1576</v>
       </c>
-    </row>
-    <row r="52" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A52" s="2">
         <v>37009</v>
       </c>
@@ -30235,8 +30392,11 @@
       <c r="S52" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="53" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A53" s="2">
         <v>37009</v>
       </c>
@@ -30294,8 +30454,11 @@
       <c r="S53" t="s">
         <v>1576</v>
       </c>
-    </row>
-    <row r="54" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A54" s="2">
         <v>37009</v>
       </c>
@@ -30353,8 +30516,11 @@
       <c r="S54" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="55" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A55" s="2">
         <v>37009</v>
       </c>
@@ -30412,8 +30578,11 @@
       <c r="S55" t="s">
         <v>1576</v>
       </c>
-    </row>
-    <row r="56" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A56" s="2">
         <v>37009</v>
       </c>
@@ -30471,8 +30640,11 @@
       <c r="S56" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="57" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A57" s="2">
         <v>37009</v>
       </c>
@@ -30530,8 +30702,11 @@
       <c r="S57" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="58" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A58" s="2">
         <v>37027</v>
       </c>
@@ -30589,8 +30764,11 @@
       <c r="S58" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="59" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A59" s="2">
         <v>37027</v>
       </c>
@@ -30648,8 +30826,11 @@
       <c r="S59" t="s">
         <v>1576</v>
       </c>
-    </row>
-    <row r="60" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A60" s="2">
         <v>37027</v>
       </c>
@@ -30707,8 +30888,11 @@
       <c r="S60" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="61" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A61" s="2">
         <v>37027</v>
       </c>
@@ -30766,8 +30950,11 @@
       <c r="S61" t="s">
         <v>1576</v>
       </c>
-    </row>
-    <row r="62" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A62" s="2">
         <v>37027</v>
       </c>
@@ -30825,8 +31012,11 @@
       <c r="S62" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="63" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A63" s="2">
         <v>37027</v>
       </c>
@@ -30884,8 +31074,11 @@
       <c r="S63" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="64" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A64" s="2">
         <v>37027</v>
       </c>
@@ -30943,8 +31136,11 @@
       <c r="S64" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="65" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A65" s="2">
         <v>37027</v>
       </c>
@@ -31002,8 +31198,11 @@
       <c r="S65" t="s">
         <v>1578</v>
       </c>
-    </row>
-    <row r="66" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A66" s="2">
         <v>37027</v>
       </c>
@@ -31061,8 +31260,11 @@
       <c r="S66" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="67" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A67" s="2">
         <v>37027</v>
       </c>
@@ -31120,8 +31322,11 @@
       <c r="S67" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="68" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A68" s="2">
         <v>37027</v>
       </c>
@@ -31179,8 +31384,11 @@
       <c r="S68" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="69" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A69" s="2">
         <v>37027</v>
       </c>
@@ -31238,8 +31446,11 @@
       <c r="S69" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="70" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A70" s="2">
         <v>37027</v>
       </c>
@@ -31297,8 +31508,11 @@
       <c r="S70" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="71" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A71" s="2">
         <v>37027</v>
       </c>
@@ -31356,8 +31570,11 @@
       <c r="S71" t="s">
         <v>1576</v>
       </c>
-    </row>
-    <row r="72" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A72" s="2">
         <v>37027</v>
       </c>
@@ -31415,8 +31632,11 @@
       <c r="S72" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="73" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A73" s="2">
         <v>37027</v>
       </c>
@@ -31474,8 +31694,11 @@
       <c r="S73" t="s">
         <v>1576</v>
       </c>
-    </row>
-    <row r="74" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A74" s="2">
         <v>37027</v>
       </c>
@@ -31533,8 +31756,11 @@
       <c r="S74" t="s">
         <v>1578</v>
       </c>
-    </row>
-    <row r="75" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A75" s="2">
         <v>37027</v>
       </c>
@@ -31592,8 +31818,11 @@
       <c r="S75" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="76" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A76" s="2">
         <v>37027</v>
       </c>
@@ -31651,8 +31880,11 @@
       <c r="S76" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="77" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A77" s="2">
         <v>37033</v>
       </c>
@@ -31710,8 +31942,11 @@
       <c r="S77" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="78" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A78" s="2">
         <v>37033</v>
       </c>
@@ -31769,8 +32004,11 @@
       <c r="S78" t="s">
         <v>1576</v>
       </c>
-    </row>
-    <row r="79" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A79" s="2">
         <v>37033</v>
       </c>
@@ -31828,8 +32066,11 @@
       <c r="S79" t="s">
         <v>1576</v>
       </c>
-    </row>
-    <row r="80" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A80" s="2">
         <v>37033</v>
       </c>
@@ -31887,8 +32128,11 @@
       <c r="S80" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="81" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A81" s="2">
         <v>37033</v>
       </c>
@@ -31946,8 +32190,11 @@
       <c r="S81" t="s">
         <v>1576</v>
       </c>
-    </row>
-    <row r="82" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A82" s="2">
         <v>37033</v>
       </c>
@@ -32005,8 +32252,11 @@
       <c r="S82" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="83" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A83" s="2">
         <v>37057</v>
       </c>
@@ -32064,8 +32314,11 @@
       <c r="S83" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="84" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A84" s="2">
         <v>37057</v>
       </c>
@@ -32123,8 +32376,11 @@
       <c r="S84" t="s">
         <v>1576</v>
       </c>
-    </row>
-    <row r="85" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A85" s="2">
         <v>37057</v>
       </c>
@@ -32182,8 +32438,11 @@
       <c r="S85" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="86" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A86" s="2">
         <v>37057</v>
       </c>
@@ -32241,8 +32500,11 @@
       <c r="S86" t="s">
         <v>1576</v>
       </c>
-    </row>
-    <row r="87" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A87" s="2">
         <v>37057</v>
       </c>
@@ -32300,8 +32562,11 @@
       <c r="S87" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="88" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A88" s="2">
         <v>37057</v>
       </c>
@@ -32359,8 +32624,11 @@
       <c r="S88" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="89" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A89" s="2">
         <v>37057</v>
       </c>
@@ -32418,8 +32686,11 @@
       <c r="S89" t="s">
         <v>1576</v>
       </c>
-    </row>
-    <row r="90" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A90" s="2">
         <v>37057</v>
       </c>
@@ -32477,8 +32748,11 @@
       <c r="S90" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="91" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A91" s="2">
         <v>37057</v>
       </c>
@@ -32536,8 +32810,11 @@
       <c r="S91" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="92" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A92" s="2">
         <v>37057</v>
       </c>
@@ -32595,8 +32872,11 @@
       <c r="S92" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="93" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A93" s="2">
         <v>37057</v>
       </c>
@@ -32654,8 +32934,11 @@
       <c r="S93" t="s">
         <v>1576</v>
       </c>
-    </row>
-    <row r="94" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A94" s="2">
         <v>37057</v>
       </c>
@@ -32713,8 +32996,11 @@
       <c r="S94" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="95" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A95" s="2">
         <v>37057</v>
       </c>
@@ -32772,8 +33058,11 @@
       <c r="S95" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="96" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A96" s="2">
         <v>37057</v>
       </c>
@@ -32831,8 +33120,11 @@
       <c r="S96" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="97" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A97" s="2">
         <v>37057</v>
       </c>
@@ -32890,8 +33182,11 @@
       <c r="S97" t="s">
         <v>1576</v>
       </c>
-    </row>
-    <row r="98" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A98" s="2">
         <v>37057</v>
       </c>
@@ -32949,8 +33244,11 @@
       <c r="S98" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="99" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A99" s="2">
         <v>37057</v>
       </c>
@@ -33008,8 +33306,11 @@
       <c r="S99" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="100" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A100" s="2">
         <v>37057</v>
       </c>
@@ -33067,8 +33368,11 @@
       <c r="S100" t="s">
         <v>1576</v>
       </c>
-    </row>
-    <row r="101" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A101" s="2">
         <v>37057</v>
       </c>
@@ -33126,8 +33430,11 @@
       <c r="S101" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="102" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T101">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A102" s="2">
         <v>37057</v>
       </c>
@@ -33185,8 +33492,11 @@
       <c r="S102" t="s">
         <v>1576</v>
       </c>
-    </row>
-    <row r="103" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T102">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A103" s="2">
         <v>37057</v>
       </c>
@@ -33244,8 +33554,11 @@
       <c r="S103" t="s">
         <v>1576</v>
       </c>
-    </row>
-    <row r="104" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T103">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A104" s="2">
         <v>37057</v>
       </c>
@@ -33303,8 +33616,11 @@
       <c r="S104" t="s">
         <v>1576</v>
       </c>
-    </row>
-    <row r="105" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T104">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A105" s="2">
         <v>37057</v>
       </c>
@@ -33362,8 +33678,11 @@
       <c r="S105" t="s">
         <v>1576</v>
       </c>
-    </row>
-    <row r="106" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T105">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A106" s="2">
         <v>37057</v>
       </c>
@@ -33421,8 +33740,11 @@
       <c r="S106" t="s">
         <v>1576</v>
       </c>
-    </row>
-    <row r="107" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T106">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A107" s="2">
         <v>37057</v>
       </c>
@@ -33480,8 +33802,11 @@
       <c r="S107" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="108" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T107">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A108" s="2">
         <v>37057</v>
       </c>
@@ -33539,8 +33864,11 @@
       <c r="S108" t="s">
         <v>1576</v>
       </c>
-    </row>
-    <row r="109" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T108">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A109" s="2">
         <v>37057</v>
       </c>
@@ -33598,8 +33926,11 @@
       <c r="S109" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="110" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T109">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A110" s="2">
         <v>37057</v>
       </c>
@@ -33657,8 +33988,11 @@
       <c r="S110" t="s">
         <v>1576</v>
       </c>
-    </row>
-    <row r="111" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T110">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A111" s="2">
         <v>37057</v>
       </c>
@@ -33716,8 +34050,11 @@
       <c r="S111" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="112" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T111">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A112" s="2">
         <v>37057</v>
       </c>
@@ -33775,8 +34112,11 @@
       <c r="S112" t="s">
         <v>1578</v>
       </c>
-    </row>
-    <row r="113" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T112">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A113" s="2">
         <v>37057</v>
       </c>
@@ -33834,8 +34174,11 @@
       <c r="S113" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="114" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T113">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A114" s="2">
         <v>37057</v>
       </c>
@@ -33893,8 +34236,11 @@
       <c r="S114" t="s">
         <v>1576</v>
       </c>
-    </row>
-    <row r="115" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T114">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A115" s="2">
         <v>37057</v>
       </c>
@@ -33952,8 +34298,11 @@
       <c r="S115" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="116" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T115">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A116" s="2">
         <v>37057</v>
       </c>
@@ -34011,8 +34360,11 @@
       <c r="S116" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="117" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T116">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A117" s="2">
         <v>37057</v>
       </c>
@@ -34070,8 +34422,11 @@
       <c r="S117" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="118" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T117">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A118" s="2">
         <v>37057</v>
       </c>
@@ -34129,8 +34484,11 @@
       <c r="S118" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="119" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T118">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A119" s="2">
         <v>37057</v>
       </c>
@@ -34188,8 +34546,11 @@
       <c r="S119" t="s">
         <v>1576</v>
       </c>
-    </row>
-    <row r="120" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T119">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A120" s="2">
         <v>37057</v>
       </c>
@@ -34247,8 +34608,11 @@
       <c r="S120" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="121" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T120">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A121" s="2">
         <v>37057</v>
       </c>
@@ -34306,8 +34670,11 @@
       <c r="S121" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="122" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T121">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A122" s="2">
         <v>37057</v>
       </c>
@@ -34365,8 +34732,11 @@
       <c r="S122" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="123" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T122">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A123" s="2">
         <v>37057</v>
       </c>
@@ -34424,8 +34794,11 @@
       <c r="S123" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="124" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T123">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A124" s="2">
         <v>37057</v>
       </c>
@@ -34483,8 +34856,11 @@
       <c r="S124" t="s">
         <v>1576</v>
       </c>
-    </row>
-    <row r="125" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T124">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A125" s="2">
         <v>37059</v>
       </c>
@@ -34542,8 +34918,11 @@
       <c r="S125" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="126" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T125">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A126" s="2">
         <v>37059</v>
       </c>
@@ -34601,8 +34980,11 @@
       <c r="S126" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="127" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T126">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A127" s="2">
         <v>37059</v>
       </c>
@@ -34660,8 +35042,11 @@
       <c r="S127" t="s">
         <v>1576</v>
       </c>
-    </row>
-    <row r="128" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T127">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A128" s="2">
         <v>37059</v>
       </c>
@@ -34719,8 +35104,11 @@
       <c r="S128" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="129" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T128">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A129" s="2">
         <v>37059</v>
       </c>
@@ -34778,8 +35166,11 @@
       <c r="S129" t="s">
         <v>1576</v>
       </c>
-    </row>
-    <row r="130" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T129">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A130" s="2">
         <v>37059</v>
       </c>
@@ -34837,8 +35228,11 @@
       <c r="S130" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="131" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T130">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A131" s="2">
         <v>37059</v>
       </c>
@@ -34896,8 +35290,11 @@
       <c r="S131" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="132" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T131">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A132" s="2">
         <v>37059</v>
       </c>
@@ -34955,8 +35352,11 @@
       <c r="S132" t="s">
         <v>1576</v>
       </c>
-    </row>
-    <row r="133" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T132">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A133" s="2">
         <v>37059</v>
       </c>
@@ -35014,8 +35414,11 @@
       <c r="S133" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="134" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T133">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A134" s="2">
         <v>37059</v>
       </c>
@@ -35073,8 +35476,11 @@
       <c r="S134" t="s">
         <v>1576</v>
       </c>
-    </row>
-    <row r="135" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T134">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="135" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A135" s="2">
         <v>37067</v>
       </c>
@@ -35132,8 +35538,11 @@
       <c r="S135" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="136" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T135">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="136" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A136" s="2">
         <v>37067</v>
       </c>
@@ -35191,8 +35600,11 @@
       <c r="S136" t="s">
         <v>1576</v>
       </c>
-    </row>
-    <row r="137" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T136">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="137" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A137" s="2">
         <v>37067</v>
       </c>
@@ -35250,8 +35662,11 @@
       <c r="S137" t="s">
         <v>1576</v>
       </c>
-    </row>
-    <row r="138" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T137">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="138" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A138" s="2">
         <v>37067</v>
       </c>
@@ -35309,8 +35724,11 @@
       <c r="S138" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="139" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T138">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="139" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A139" s="2">
         <v>37067</v>
       </c>
@@ -35368,8 +35786,11 @@
       <c r="S139" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="140" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T139">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="140" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A140" s="2">
         <v>37067</v>
       </c>
@@ -35427,8 +35848,11 @@
       <c r="S140" t="s">
         <v>1576</v>
       </c>
-    </row>
-    <row r="141" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T140">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="141" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A141" s="2">
         <v>37067</v>
       </c>
@@ -35486,8 +35910,11 @@
       <c r="S141" t="s">
         <v>1576</v>
       </c>
-    </row>
-    <row r="142" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T141">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="142" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A142" s="2">
         <v>37067</v>
       </c>
@@ -35545,8 +35972,11 @@
       <c r="S142" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="143" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T142">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="143" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A143" s="2">
         <v>37067</v>
       </c>
@@ -35604,8 +36034,11 @@
       <c r="S143" t="s">
         <v>1576</v>
       </c>
-    </row>
-    <row r="144" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T143">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="144" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A144" s="2">
         <v>37067</v>
       </c>
@@ -35663,8 +36096,11 @@
       <c r="S144" t="s">
         <v>1576</v>
       </c>
-    </row>
-    <row r="145" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T144">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="145" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A145" s="2">
         <v>37067</v>
       </c>
@@ -35722,8 +36158,11 @@
       <c r="S145" t="s">
         <v>1576</v>
       </c>
-    </row>
-    <row r="146" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T145">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="146" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A146" s="2">
         <v>37067</v>
       </c>
@@ -35781,8 +36220,11 @@
       <c r="S146" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="147" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T146">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="147" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A147" s="2">
         <v>37067</v>
       </c>
@@ -35840,8 +36282,11 @@
       <c r="S147" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="148" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T147">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="148" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A148" s="2">
         <v>37067</v>
       </c>
@@ -35899,8 +36344,11 @@
       <c r="S148" t="s">
         <v>1576</v>
       </c>
-    </row>
-    <row r="149" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T148">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="149" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A149" s="2">
         <v>37067</v>
       </c>
@@ -35958,8 +36406,11 @@
       <c r="S149" t="s">
         <v>1576</v>
       </c>
-    </row>
-    <row r="150" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T149">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="150" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A150" s="2">
         <v>37067</v>
       </c>
@@ -36017,8 +36468,11 @@
       <c r="S150" t="s">
         <v>1576</v>
       </c>
-    </row>
-    <row r="151" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T150">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="151" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A151" s="2">
         <v>37067</v>
       </c>
@@ -36076,8 +36530,11 @@
       <c r="S151" t="s">
         <v>1576</v>
       </c>
-    </row>
-    <row r="152" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T151">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="152" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A152" s="2">
         <v>37067</v>
       </c>
@@ -36135,8 +36592,11 @@
       <c r="S152" t="s">
         <v>1576</v>
       </c>
-    </row>
-    <row r="153" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T152">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="153" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A153" s="2">
         <v>37067</v>
       </c>
@@ -36194,8 +36654,11 @@
       <c r="S153" t="s">
         <v>1576</v>
       </c>
-    </row>
-    <row r="154" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T153">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="154" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A154" s="2">
         <v>37067</v>
       </c>
@@ -36253,8 +36716,11 @@
       <c r="S154" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="155" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T154">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="155" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A155" s="2">
         <v>37067</v>
       </c>
@@ -36312,8 +36778,11 @@
       <c r="S155" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="156" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T155">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="156" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A156" s="2">
         <v>37067</v>
       </c>
@@ -36371,8 +36840,11 @@
       <c r="S156" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="157" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T156">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="157" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A157" s="2">
         <v>37067</v>
       </c>
@@ -36430,8 +36902,11 @@
       <c r="S157" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="158" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T157">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="158" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A158" s="2">
         <v>37067</v>
       </c>
@@ -36489,8 +36964,11 @@
       <c r="S158" t="s">
         <v>1576</v>
       </c>
-    </row>
-    <row r="159" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T158">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="159" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A159" s="2">
         <v>37067</v>
       </c>
@@ -36548,8 +37026,11 @@
       <c r="S159" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="160" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T159">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="160" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A160" s="2">
         <v>37067</v>
       </c>
@@ -36607,8 +37088,11 @@
       <c r="S160" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="161" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T160">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="161" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A161" s="2">
         <v>37067</v>
       </c>
@@ -36666,8 +37150,11 @@
       <c r="S161" t="s">
         <v>1576</v>
       </c>
-    </row>
-    <row r="162" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T161">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="162" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A162" s="2">
         <v>37067</v>
       </c>
@@ -36725,8 +37212,11 @@
       <c r="S162" t="s">
         <v>1576</v>
       </c>
-    </row>
-    <row r="163" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T162">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="163" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A163" s="2">
         <v>37067</v>
       </c>
@@ -36784,8 +37274,11 @@
       <c r="S163" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="164" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T163">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="164" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A164" s="2">
         <v>37067</v>
       </c>
@@ -36843,8 +37336,11 @@
       <c r="S164" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="165" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T164">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="165" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A165" s="2">
         <v>37067</v>
       </c>
@@ -36902,8 +37398,11 @@
       <c r="S165" t="s">
         <v>1578</v>
       </c>
-    </row>
-    <row r="166" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T165">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="166" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A166" s="2">
         <v>37067</v>
       </c>
@@ -36961,8 +37460,11 @@
       <c r="S166" t="s">
         <v>1579</v>
       </c>
-    </row>
-    <row r="167" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T166">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="167" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A167" s="2">
         <v>37067</v>
       </c>
@@ -37020,8 +37522,11 @@
       <c r="S167" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="168" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T167">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="168" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A168" s="2">
         <v>37067</v>
       </c>
@@ -37079,8 +37584,11 @@
       <c r="S168" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="169" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T168">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="169" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A169" s="2">
         <v>37067</v>
       </c>
@@ -37138,8 +37646,11 @@
       <c r="S169" t="s">
         <v>1576</v>
       </c>
-    </row>
-    <row r="170" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T169">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="170" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A170" s="2">
         <v>37067</v>
       </c>
@@ -37197,8 +37708,11 @@
       <c r="S170" t="s">
         <v>1576</v>
       </c>
-    </row>
-    <row r="171" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T170">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="171" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A171" s="2">
         <v>37067</v>
       </c>
@@ -37256,8 +37770,11 @@
       <c r="S171" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="172" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T171">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="172" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A172" s="2">
         <v>37067</v>
       </c>
@@ -37315,8 +37832,11 @@
       <c r="S172" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="173" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T172">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="173" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A173" s="2">
         <v>37067</v>
       </c>
@@ -37374,8 +37894,11 @@
       <c r="S173" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="174" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T173">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="174" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A174" s="2">
         <v>37067</v>
       </c>
@@ -37433,8 +37956,11 @@
       <c r="S174" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="175" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T174">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="175" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A175" s="2">
         <v>37067</v>
       </c>
@@ -37492,8 +38018,11 @@
       <c r="S175" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="176" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T175">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="176" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A176" s="2">
         <v>37067</v>
       </c>
@@ -37551,8 +38080,11 @@
       <c r="S176" t="s">
         <v>1576</v>
       </c>
-    </row>
-    <row r="177" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T176">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="177" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A177" s="2">
         <v>37067</v>
       </c>
@@ -37610,8 +38142,11 @@
       <c r="S177" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="178" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T177">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="178" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A178" s="2">
         <v>37067</v>
       </c>
@@ -37669,8 +38204,11 @@
       <c r="S178" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="179" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T178">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="179" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A179" s="2">
         <v>37067</v>
       </c>
@@ -37728,8 +38266,11 @@
       <c r="S179" t="s">
         <v>1576</v>
       </c>
-    </row>
-    <row r="180" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T179">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="180" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A180" s="2">
         <v>37067</v>
       </c>
@@ -37787,8 +38328,11 @@
       <c r="S180" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="181" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T180">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="181" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A181" s="2">
         <v>37067</v>
       </c>
@@ -37846,8 +38390,11 @@
       <c r="S181" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="182" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T181">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="182" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A182" s="2">
         <v>37067</v>
       </c>
@@ -37905,8 +38452,11 @@
       <c r="S182" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="183" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T182">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="183" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A183" s="2">
         <v>37067</v>
       </c>
@@ -37964,8 +38514,11 @@
       <c r="S183" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="184" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T183">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="184" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A184" s="2">
         <v>37067</v>
       </c>
@@ -38023,8 +38576,11 @@
       <c r="S184" t="s">
         <v>1576</v>
       </c>
-    </row>
-    <row r="185" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T184">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="185" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A185" s="2">
         <v>37067</v>
       </c>
@@ -38082,8 +38638,11 @@
       <c r="S185" t="s">
         <v>1576</v>
       </c>
-    </row>
-    <row r="186" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T185">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="186" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A186" s="2">
         <v>37067</v>
       </c>
@@ -38141,8 +38700,11 @@
       <c r="S186" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="187" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T186">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="187" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A187" s="2">
         <v>37067</v>
       </c>
@@ -38200,8 +38762,11 @@
       <c r="S187" t="s">
         <v>1576</v>
       </c>
-    </row>
-    <row r="188" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T187">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="188" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A188" s="2">
         <v>37067</v>
       </c>
@@ -38259,8 +38824,11 @@
       <c r="S188" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="189" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T188">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="189" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A189" s="2">
         <v>37067</v>
       </c>
@@ -38318,8 +38886,11 @@
       <c r="S189" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="190" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T189">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="190" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A190" s="2">
         <v>37067</v>
       </c>
@@ -38377,8 +38948,11 @@
       <c r="S190" t="s">
         <v>1576</v>
       </c>
-    </row>
-    <row r="191" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T190">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="191" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A191" s="2">
         <v>37067</v>
       </c>
@@ -38436,8 +39010,11 @@
       <c r="S191" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="192" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T191">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="192" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A192" s="2">
         <v>37067</v>
       </c>
@@ -38495,8 +39072,11 @@
       <c r="S192" t="s">
         <v>1578</v>
       </c>
-    </row>
-    <row r="193" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T192">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="193" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A193" s="2">
         <v>37067</v>
       </c>
@@ -38554,8 +39134,11 @@
       <c r="S193" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="194" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T193">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="194" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A194" s="2">
         <v>37067</v>
       </c>
@@ -38613,8 +39196,11 @@
       <c r="S194" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="195" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T194">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="195" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A195" s="2">
         <v>37067</v>
       </c>
@@ -38672,8 +39258,11 @@
       <c r="S195" t="s">
         <v>1579</v>
       </c>
-    </row>
-    <row r="196" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T195">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="196" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A196" s="2">
         <v>37067</v>
       </c>
@@ -38731,8 +39320,11 @@
       <c r="S196" t="s">
         <v>1579</v>
       </c>
-    </row>
-    <row r="197" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T196">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="197" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A197" s="2">
         <v>37067</v>
       </c>
@@ -38790,8 +39382,11 @@
       <c r="S197" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="198" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T197">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="198" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A198" s="2">
         <v>37067</v>
       </c>
@@ -38849,8 +39444,11 @@
       <c r="S198" t="s">
         <v>1579</v>
       </c>
-    </row>
-    <row r="199" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T198">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="199" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A199" s="2">
         <v>37067</v>
       </c>
@@ -38908,8 +39506,11 @@
       <c r="S199" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="200" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T199">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="200" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A200" s="2">
         <v>37067</v>
       </c>
@@ -38967,8 +39568,11 @@
       <c r="S200" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="201" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T200">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="201" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A201" s="2">
         <v>37067</v>
       </c>
@@ -39026,8 +39630,11 @@
       <c r="S201" t="s">
         <v>1576</v>
       </c>
-    </row>
-    <row r="202" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T201">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="202" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A202" s="2">
         <v>37067</v>
       </c>
@@ -39085,8 +39692,11 @@
       <c r="S202" t="s">
         <v>1576</v>
       </c>
-    </row>
-    <row r="203" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T202">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="203" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A203" s="2">
         <v>37067</v>
       </c>
@@ -39144,8 +39754,11 @@
       <c r="S203" t="s">
         <v>1576</v>
       </c>
-    </row>
-    <row r="204" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T203">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="204" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A204" s="2">
         <v>37067</v>
       </c>
@@ -39203,8 +39816,11 @@
       <c r="S204" t="s">
         <v>1576</v>
       </c>
-    </row>
-    <row r="205" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T204">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="205" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A205" s="2">
         <v>37067</v>
       </c>
@@ -39262,8 +39878,11 @@
       <c r="S205" t="s">
         <v>1576</v>
       </c>
-    </row>
-    <row r="206" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T205">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="206" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A206" s="2">
         <v>37067</v>
       </c>
@@ -39321,8 +39940,11 @@
       <c r="S206" t="s">
         <v>1576</v>
       </c>
-    </row>
-    <row r="207" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T206">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="207" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A207" s="2">
         <v>37067</v>
       </c>
@@ -39380,8 +40002,11 @@
       <c r="S207" t="s">
         <v>1576</v>
       </c>
-    </row>
-    <row r="208" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T207">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="208" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A208" s="2">
         <v>37067</v>
       </c>
@@ -39439,8 +40064,11 @@
       <c r="S208" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="209" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T208">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="209" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A209" s="2">
         <v>37067</v>
       </c>
@@ -39498,8 +40126,11 @@
       <c r="S209" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="210" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T209">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="210" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A210" s="2">
         <v>37067</v>
       </c>
@@ -39557,8 +40188,11 @@
       <c r="S210" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="211" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T210">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="211" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A211" s="2">
         <v>37067</v>
       </c>
@@ -39616,8 +40250,11 @@
       <c r="S211" t="s">
         <v>1576</v>
       </c>
-    </row>
-    <row r="212" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T211">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="212" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A212" s="2">
         <v>37067</v>
       </c>
@@ -39675,8 +40312,11 @@
       <c r="S212" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="213" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T212">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="213" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A213" s="2">
         <v>37067</v>
       </c>
@@ -39734,8 +40374,11 @@
       <c r="S213" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="214" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T213">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="214" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A214" s="2">
         <v>37067</v>
       </c>
@@ -39793,8 +40436,11 @@
       <c r="S214" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="215" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T214">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="215" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A215" s="2">
         <v>37067</v>
       </c>
@@ -39852,8 +40498,11 @@
       <c r="S215" t="s">
         <v>1576</v>
       </c>
-    </row>
-    <row r="216" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T215">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="216" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A216" s="2">
         <v>37067</v>
       </c>
@@ -39911,8 +40560,11 @@
       <c r="S216" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="217" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T216">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="217" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A217" s="2">
         <v>37067</v>
       </c>
@@ -39970,8 +40622,11 @@
       <c r="S217" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="218" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T217">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="218" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A218" s="2">
         <v>37067</v>
       </c>
@@ -40029,8 +40684,11 @@
       <c r="S218" t="s">
         <v>1576</v>
       </c>
-    </row>
-    <row r="219" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T218">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="219" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A219" s="2">
         <v>37067</v>
       </c>
@@ -40088,8 +40746,11 @@
       <c r="S219" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="220" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T219">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="220" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A220" s="2">
         <v>37067</v>
       </c>
@@ -40147,8 +40808,11 @@
       <c r="S220" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="221" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T220">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="221" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A221" s="2">
         <v>37067</v>
       </c>
@@ -40206,8 +40870,11 @@
       <c r="S221" t="s">
         <v>1579</v>
       </c>
-    </row>
-    <row r="222" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T221">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="222" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A222" s="2">
         <v>37067</v>
       </c>
@@ -40265,8 +40932,11 @@
       <c r="S222" t="s">
         <v>1579</v>
       </c>
-    </row>
-    <row r="223" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T222">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="223" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A223" s="2">
         <v>37067</v>
       </c>
@@ -40324,8 +40994,11 @@
       <c r="S223" t="s">
         <v>1578</v>
       </c>
-    </row>
-    <row r="224" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T223">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="224" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A224" s="2">
         <v>37067</v>
       </c>
@@ -40383,8 +41056,11 @@
       <c r="S224" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="225" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T224">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="225" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A225" s="2">
         <v>37067</v>
       </c>
@@ -40442,8 +41118,11 @@
       <c r="S225" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="226" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T225">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="226" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A226" s="2">
         <v>37067</v>
       </c>
@@ -40501,8 +41180,11 @@
       <c r="S226" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="227" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T226">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="227" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A227" s="2">
         <v>37067</v>
       </c>
@@ -40560,8 +41242,11 @@
       <c r="S227" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="228" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T227">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="228" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A228" s="2">
         <v>37067</v>
       </c>
@@ -40619,8 +41304,11 @@
       <c r="S228" t="s">
         <v>1579</v>
       </c>
-    </row>
-    <row r="229" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T228">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="229" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A229" s="2">
         <v>37067</v>
       </c>
@@ -40678,8 +41366,11 @@
       <c r="S229" t="s">
         <v>1579</v>
       </c>
-    </row>
-    <row r="230" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T229">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="230" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A230" s="2">
         <v>37081</v>
       </c>
@@ -40737,8 +41428,11 @@
       <c r="S230" t="s">
         <v>1576</v>
       </c>
-    </row>
-    <row r="231" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T230">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="231" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A231" s="2">
         <v>37081</v>
       </c>
@@ -40796,8 +41490,11 @@
       <c r="S231" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="232" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T231">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="232" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A232" s="2">
         <v>37081</v>
       </c>
@@ -40855,8 +41552,11 @@
       <c r="S232" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="233" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T232">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="233" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A233" s="2">
         <v>37081</v>
       </c>
@@ -40914,8 +41614,11 @@
       <c r="S233" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="234" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T233">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="234" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A234" s="2">
         <v>37081</v>
       </c>
@@ -40973,8 +41676,11 @@
       <c r="S234" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="235" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T234">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="235" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A235" s="2">
         <v>37081</v>
       </c>
@@ -41032,8 +41738,11 @@
       <c r="S235" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="236" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T235">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="236" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A236" s="2">
         <v>37081</v>
       </c>
@@ -41091,8 +41800,11 @@
       <c r="S236" t="s">
         <v>1576</v>
       </c>
-    </row>
-    <row r="237" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T236">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="237" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A237" s="2">
         <v>37081</v>
       </c>
@@ -41150,8 +41862,11 @@
       <c r="S237" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="238" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T237">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="238" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A238" s="2">
         <v>37081</v>
       </c>
@@ -41209,8 +41924,11 @@
       <c r="S238" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="239" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T238">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="239" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A239" s="2">
         <v>37081</v>
       </c>
@@ -41268,8 +41986,11 @@
       <c r="S239" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="240" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T239">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="240" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A240" s="2">
         <v>37081</v>
       </c>
@@ -41327,8 +42048,11 @@
       <c r="S240" t="s">
         <v>1576</v>
       </c>
-    </row>
-    <row r="241" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T240">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="241" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A241" s="2">
         <v>37081</v>
       </c>
@@ -41386,8 +42110,11 @@
       <c r="S241" t="s">
         <v>1576</v>
       </c>
-    </row>
-    <row r="242" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T241">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="242" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A242" s="2">
         <v>37081</v>
       </c>
@@ -41445,8 +42172,11 @@
       <c r="S242" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="243" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T242">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="243" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A243" s="2">
         <v>37081</v>
       </c>
@@ -41504,8 +42234,11 @@
       <c r="S243" t="s">
         <v>1576</v>
       </c>
-    </row>
-    <row r="244" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T243">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="244" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A244" s="2">
         <v>37081</v>
       </c>
@@ -41563,8 +42296,11 @@
       <c r="S244" t="s">
         <v>1576</v>
       </c>
-    </row>
-    <row r="245" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T244">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="245" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A245" s="2">
         <v>37081</v>
       </c>
@@ -41622,8 +42358,11 @@
       <c r="S245" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="246" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T245">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="246" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A246" s="2">
         <v>37081</v>
       </c>
@@ -41681,8 +42420,11 @@
       <c r="S246" t="s">
         <v>1576</v>
       </c>
-    </row>
-    <row r="247" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T246">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="247" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A247" s="2">
         <v>37081</v>
       </c>
@@ -41740,8 +42482,11 @@
       <c r="S247" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="248" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T247">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="248" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A248" s="2">
         <v>37081</v>
       </c>
@@ -41799,8 +42544,11 @@
       <c r="S248" t="s">
         <v>1576</v>
       </c>
-    </row>
-    <row r="249" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T248">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="249" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A249" s="2">
         <v>37081</v>
       </c>
@@ -41858,8 +42606,11 @@
       <c r="S249" t="s">
         <v>1576</v>
       </c>
-    </row>
-    <row r="250" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T249">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="250" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A250" s="2">
         <v>37081</v>
       </c>
@@ -41917,8 +42668,11 @@
       <c r="S250" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="251" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T250">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="251" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A251" s="2">
         <v>37081</v>
       </c>
@@ -41976,8 +42730,11 @@
       <c r="S251" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="252" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T251">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="252" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A252" s="2">
         <v>37081</v>
       </c>
@@ -42035,8 +42792,11 @@
       <c r="S252" t="s">
         <v>1576</v>
       </c>
-    </row>
-    <row r="253" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T252">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="253" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A253" s="2">
         <v>37081</v>
       </c>
@@ -42094,8 +42854,11 @@
       <c r="S253" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="254" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T253">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="254" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A254" s="2">
         <v>37081</v>
       </c>
@@ -42153,8 +42916,11 @@
       <c r="S254" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="255" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T254">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="255" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A255" s="2">
         <v>37081</v>
       </c>
@@ -42212,8 +42978,11 @@
       <c r="S255" t="s">
         <v>1576</v>
       </c>
-    </row>
-    <row r="256" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T255">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="256" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A256" s="2">
         <v>37081</v>
       </c>
@@ -42271,8 +43040,11 @@
       <c r="S256" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="257" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T256">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="257" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A257" s="2">
         <v>37081</v>
       </c>
@@ -42330,8 +43102,11 @@
       <c r="S257" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="258" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T257">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="258" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A258" s="2">
         <v>37081</v>
       </c>
@@ -42389,8 +43164,11 @@
       <c r="S258" t="s">
         <v>1576</v>
       </c>
-    </row>
-    <row r="259" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T258">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="259" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A259" s="2">
         <v>37081</v>
       </c>
@@ -42448,8 +43226,11 @@
       <c r="S259" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="260" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T259">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="260" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A260" s="2">
         <v>37081</v>
       </c>
@@ -42507,8 +43288,11 @@
       <c r="S260" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="261" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T260">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="261" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A261" s="2">
         <v>37081</v>
       </c>
@@ -42566,8 +43350,11 @@
       <c r="S261" t="s">
         <v>1579</v>
       </c>
-    </row>
-    <row r="262" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T261">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="262" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A262" s="2">
         <v>37081</v>
       </c>
@@ -42625,8 +43412,11 @@
       <c r="S262" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="263" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T262">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="263" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A263" s="2">
         <v>37081</v>
       </c>
@@ -42684,8 +43474,11 @@
       <c r="S263" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="264" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T263">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="264" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A264" s="2">
         <v>37081</v>
       </c>
@@ -42743,8 +43536,11 @@
       <c r="S264" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="265" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T264">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="265" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A265" s="2">
         <v>37081</v>
       </c>
@@ -42802,8 +43598,11 @@
       <c r="S265" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="266" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T265">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="266" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A266" s="2">
         <v>37081</v>
       </c>
@@ -42861,8 +43660,11 @@
       <c r="S266" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="267" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T266">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="267" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A267" s="2">
         <v>37081</v>
       </c>
@@ -42920,8 +43722,11 @@
       <c r="S267" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="268" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T267">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="268" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A268" s="2">
         <v>37081</v>
       </c>
@@ -42979,8 +43784,11 @@
       <c r="S268" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="269" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T268">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="269" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A269" s="2">
         <v>37081</v>
       </c>
@@ -43038,8 +43846,11 @@
       <c r="S269" t="s">
         <v>1576</v>
       </c>
-    </row>
-    <row r="270" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T269">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="270" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A270" s="2">
         <v>37081</v>
       </c>
@@ -43097,8 +43908,11 @@
       <c r="S270" t="s">
         <v>1576</v>
       </c>
-    </row>
-    <row r="271" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T270">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="271" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A271" s="2">
         <v>37081</v>
       </c>
@@ -43156,8 +43970,11 @@
       <c r="S271" t="s">
         <v>1576</v>
       </c>
-    </row>
-    <row r="272" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T271">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="272" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A272" s="2">
         <v>37081</v>
       </c>
@@ -43215,8 +44032,11 @@
       <c r="S272" t="s">
         <v>1576</v>
       </c>
-    </row>
-    <row r="273" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T272">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="273" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A273" s="2">
         <v>37081</v>
       </c>
@@ -43274,8 +44094,11 @@
       <c r="S273" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="274" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T273">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="274" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A274" s="2">
         <v>37081</v>
       </c>
@@ -43333,8 +44156,11 @@
       <c r="S274" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="275" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T274">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="275" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A275" s="2">
         <v>37081</v>
       </c>
@@ -43392,8 +44218,11 @@
       <c r="S275" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="276" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T275">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="276" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A276" s="2">
         <v>37081</v>
       </c>
@@ -43451,8 +44280,11 @@
       <c r="S276" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="277" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T276">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="277" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A277" s="2">
         <v>37081</v>
       </c>
@@ -43510,8 +44342,11 @@
       <c r="S277" t="s">
         <v>1576</v>
       </c>
-    </row>
-    <row r="278" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T277">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="278" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A278" s="2">
         <v>37081</v>
       </c>
@@ -43569,8 +44404,11 @@
       <c r="S278" t="s">
         <v>1576</v>
       </c>
-    </row>
-    <row r="279" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T278">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="279" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A279" s="2">
         <v>37081</v>
       </c>
@@ -43628,8 +44466,11 @@
       <c r="S279" t="s">
         <v>1576</v>
       </c>
-    </row>
-    <row r="280" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T279">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="280" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A280" s="2">
         <v>37081</v>
       </c>
@@ -43687,8 +44528,11 @@
       <c r="S280" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="281" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T280">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="281" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A281" s="2">
         <v>37081</v>
       </c>
@@ -43746,8 +44590,11 @@
       <c r="S281" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="282" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T281">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="282" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A282" s="2">
         <v>37081</v>
       </c>
@@ -43805,8 +44652,11 @@
       <c r="S282" t="s">
         <v>1576</v>
       </c>
-    </row>
-    <row r="283" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T282">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="283" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A283" s="2">
         <v>37081</v>
       </c>
@@ -43864,8 +44714,11 @@
       <c r="S283" t="s">
         <v>1576</v>
       </c>
-    </row>
-    <row r="284" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T283">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="284" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A284" s="2">
         <v>37081</v>
       </c>
@@ -43923,8 +44776,11 @@
       <c r="S284" t="s">
         <v>1576</v>
       </c>
-    </row>
-    <row r="285" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T284">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="285" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A285" s="2">
         <v>37081</v>
       </c>
@@ -43982,8 +44838,11 @@
       <c r="S285" t="s">
         <v>1576</v>
       </c>
-    </row>
-    <row r="286" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T285">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="286" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A286" s="2">
         <v>37081</v>
       </c>
@@ -44041,8 +44900,11 @@
       <c r="S286" t="s">
         <v>1576</v>
       </c>
-    </row>
-    <row r="287" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T286">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="287" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A287" s="2">
         <v>37081</v>
       </c>
@@ -44100,8 +44962,11 @@
       <c r="S287" t="s">
         <v>1576</v>
       </c>
-    </row>
-    <row r="288" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T287">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="288" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A288" s="2">
         <v>37081</v>
       </c>
@@ -44159,8 +45024,11 @@
       <c r="S288" t="s">
         <v>1576</v>
       </c>
-    </row>
-    <row r="289" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T288">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="289" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A289" s="2">
         <v>37081</v>
       </c>
@@ -44218,8 +45086,11 @@
       <c r="S289" t="s">
         <v>1576</v>
       </c>
-    </row>
-    <row r="290" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T289">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="290" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A290" s="2">
         <v>37081</v>
       </c>
@@ -44277,8 +45148,11 @@
       <c r="S290" t="s">
         <v>1576</v>
       </c>
-    </row>
-    <row r="291" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T290">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="291" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A291" s="2">
         <v>37081</v>
       </c>
@@ -44336,8 +45210,11 @@
       <c r="S291" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="292" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T291">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="292" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A292" s="2">
         <v>37081</v>
       </c>
@@ -44395,8 +45272,11 @@
       <c r="S292" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="293" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T292">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="293" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A293" s="2">
         <v>37081</v>
       </c>
@@ -44454,8 +45334,11 @@
       <c r="S293" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="294" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T293">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="294" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A294" s="2">
         <v>37081</v>
       </c>
@@ -44513,8 +45396,11 @@
       <c r="S294" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="295" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T294">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="295" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A295" s="2">
         <v>37081</v>
       </c>
@@ -44572,8 +45458,11 @@
       <c r="S295" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="296" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T295">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="296" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A296" s="2">
         <v>37081</v>
       </c>
@@ -44631,8 +45520,11 @@
       <c r="S296" t="s">
         <v>1576</v>
       </c>
-    </row>
-    <row r="297" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T296">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="297" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A297" s="2">
         <v>37081</v>
       </c>
@@ -44690,8 +45582,11 @@
       <c r="S297" t="s">
         <v>1576</v>
       </c>
-    </row>
-    <row r="298" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T297">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="298" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A298" s="2">
         <v>37081</v>
       </c>
@@ -44749,8 +45644,11 @@
       <c r="S298" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="299" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T298">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="299" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A299" s="2">
         <v>37081</v>
       </c>
@@ -44808,8 +45706,11 @@
       <c r="S299" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="300" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T299">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="300" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A300" s="2">
         <v>37081</v>
       </c>
@@ -44867,8 +45768,11 @@
       <c r="S300" t="s">
         <v>1576</v>
       </c>
-    </row>
-    <row r="301" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T300">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="301" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A301" s="2">
         <v>37081</v>
       </c>
@@ -44926,8 +45830,11 @@
       <c r="S301" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="302" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T301">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="302" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A302" s="2">
         <v>37081</v>
       </c>
@@ -44985,8 +45892,11 @@
       <c r="S302" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="303" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T302">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="303" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A303" s="2">
         <v>37081</v>
       </c>
@@ -45044,8 +45954,11 @@
       <c r="S303" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="304" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T303">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="304" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A304" s="2">
         <v>37081</v>
       </c>
@@ -45103,8 +46016,11 @@
       <c r="S304" t="s">
         <v>1576</v>
       </c>
-    </row>
-    <row r="305" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T304">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="305" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A305" s="2">
         <v>37081</v>
       </c>
@@ -45162,8 +46078,11 @@
       <c r="S305" t="s">
         <v>1576</v>
       </c>
-    </row>
-    <row r="306" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T305">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="306" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A306" s="2">
         <v>37081</v>
       </c>
@@ -45221,8 +46140,11 @@
       <c r="S306" t="s">
         <v>1576</v>
       </c>
-    </row>
-    <row r="307" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T306">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="307" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A307" s="2">
         <v>37081</v>
       </c>
@@ -45280,8 +46202,11 @@
       <c r="S307" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="308" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T307">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="308" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A308" s="2">
         <v>37081</v>
       </c>
@@ -45339,8 +46264,11 @@
       <c r="S308" t="s">
         <v>1576</v>
       </c>
-    </row>
-    <row r="309" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T308">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="309" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A309" s="2">
         <v>37081</v>
       </c>
@@ -45398,8 +46326,11 @@
       <c r="S309" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="310" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T309">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="310" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A310" s="2">
         <v>37081</v>
       </c>
@@ -45457,8 +46388,11 @@
       <c r="S310" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="311" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T310">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="311" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A311" s="2">
         <v>37081</v>
       </c>
@@ -45516,8 +46450,11 @@
       <c r="S311" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="312" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T311">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="312" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A312" s="2">
         <v>37081</v>
       </c>
@@ -45575,8 +46512,11 @@
       <c r="S312" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="313" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T312">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="313" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A313" s="2">
         <v>37081</v>
       </c>
@@ -45634,8 +46574,11 @@
       <c r="S313" t="s">
         <v>1576</v>
       </c>
-    </row>
-    <row r="314" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T313">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="314" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A314" s="2">
         <v>37081</v>
       </c>
@@ -45693,8 +46636,11 @@
       <c r="S314" t="s">
         <v>1579</v>
       </c>
-    </row>
-    <row r="315" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T314">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="315" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A315" s="2">
         <v>37081</v>
       </c>
@@ -45752,8 +46698,11 @@
       <c r="S315" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="316" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T315">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="316" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A316" s="2">
         <v>37081</v>
       </c>
@@ -45811,8 +46760,11 @@
       <c r="S316" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="317" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T316">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="317" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A317" s="2">
         <v>37081</v>
       </c>
@@ -45870,8 +46822,11 @@
       <c r="S317" t="s">
         <v>1579</v>
       </c>
-    </row>
-    <row r="318" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T317">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="318" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A318" s="2">
         <v>37081</v>
       </c>
@@ -45929,8 +46884,11 @@
       <c r="S318" t="s">
         <v>1579</v>
       </c>
-    </row>
-    <row r="319" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T318">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="319" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A319" s="2">
         <v>37081</v>
       </c>
@@ -45988,8 +46946,11 @@
       <c r="S319" t="s">
         <v>1579</v>
       </c>
-    </row>
-    <row r="320" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T319">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="320" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A320" s="2">
         <v>37081</v>
       </c>
@@ -46047,8 +47008,11 @@
       <c r="S320" t="s">
         <v>1579</v>
       </c>
-    </row>
-    <row r="321" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T320">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="321" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A321" s="2">
         <v>37081</v>
       </c>
@@ -46106,8 +47070,11 @@
       <c r="S321" t="s">
         <v>1579</v>
       </c>
-    </row>
-    <row r="322" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T321">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="322" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A322" s="2">
         <v>37081</v>
       </c>
@@ -46165,8 +47132,11 @@
       <c r="S322" t="s">
         <v>1579</v>
       </c>
-    </row>
-    <row r="323" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T322">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="323" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A323" s="2">
         <v>37081</v>
       </c>
@@ -46224,8 +47194,11 @@
       <c r="S323" t="s">
         <v>1579</v>
       </c>
-    </row>
-    <row r="324" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T323">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="324" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A324" s="2">
         <v>37081</v>
       </c>
@@ -46283,8 +47256,11 @@
       <c r="S324" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="325" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T324">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="325" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A325" s="2">
         <v>37081</v>
       </c>
@@ -46342,8 +47318,11 @@
       <c r="S325" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="326" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T325">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="326" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A326" s="2">
         <v>37081</v>
       </c>
@@ -46401,8 +47380,11 @@
       <c r="S326" t="s">
         <v>1576</v>
       </c>
-    </row>
-    <row r="327" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T326">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="327" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A327" s="2">
         <v>37081</v>
       </c>
@@ -46460,8 +47442,11 @@
       <c r="S327" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="328" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T327">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="328" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A328" s="2">
         <v>37081</v>
       </c>
@@ -46519,8 +47504,11 @@
       <c r="S328" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="329" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T328">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="329" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A329" s="2">
         <v>37081</v>
       </c>
@@ -46578,8 +47566,11 @@
       <c r="S329" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="330" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T329">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="330" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A330" s="2">
         <v>37081</v>
       </c>
@@ -46637,8 +47628,11 @@
       <c r="S330" t="s">
         <v>1579</v>
       </c>
-    </row>
-    <row r="331" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T330">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="331" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A331" s="2">
         <v>37081</v>
       </c>
@@ -46696,8 +47690,11 @@
       <c r="S331" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="332" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T331">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="332" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A332" s="2">
         <v>37081</v>
       </c>
@@ -46755,8 +47752,11 @@
       <c r="S332" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="333" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T332">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="333" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A333" s="2">
         <v>37081</v>
       </c>
@@ -46814,8 +47814,11 @@
       <c r="S333" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="334" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T333">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="334" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A334" s="2">
         <v>37081</v>
       </c>
@@ -46873,8 +47876,11 @@
       <c r="S334" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="335" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T334">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="335" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A335" s="2">
         <v>37081</v>
       </c>
@@ -46932,8 +47938,11 @@
       <c r="S335" t="s">
         <v>1576</v>
       </c>
-    </row>
-    <row r="336" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T335">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="336" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A336" s="2">
         <v>37081</v>
       </c>
@@ -46991,8 +48000,11 @@
       <c r="S336" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="337" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T336">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="337" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A337" s="2">
         <v>37081</v>
       </c>
@@ -47050,8 +48062,11 @@
       <c r="S337" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="338" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T337">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="338" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A338" s="2">
         <v>37081</v>
       </c>
@@ -47109,8 +48124,11 @@
       <c r="S338" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="339" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T338">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="339" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A339" s="2">
         <v>37081</v>
       </c>
@@ -47168,8 +48186,11 @@
       <c r="S339" t="s">
         <v>1579</v>
       </c>
-    </row>
-    <row r="340" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T339">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="340" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A340" s="2">
         <v>37081</v>
       </c>
@@ -47227,8 +48248,11 @@
       <c r="S340" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="341" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T340">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="341" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A341" s="2">
         <v>37081</v>
       </c>
@@ -47286,8 +48310,11 @@
       <c r="S341" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="342" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T341">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="342" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A342" s="2">
         <v>37081</v>
       </c>
@@ -47345,8 +48372,11 @@
       <c r="S342" t="s">
         <v>1576</v>
       </c>
-    </row>
-    <row r="343" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T342">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="343" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A343" s="2">
         <v>37081</v>
       </c>
@@ -47404,8 +48434,11 @@
       <c r="S343" t="s">
         <v>1576</v>
       </c>
-    </row>
-    <row r="344" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T343">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="344" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A344" s="2">
         <v>37081</v>
       </c>
@@ -47463,8 +48496,11 @@
       <c r="S344" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="345" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T344">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="345" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A345" s="2">
         <v>37081</v>
       </c>
@@ -47522,8 +48558,11 @@
       <c r="S345" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="346" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T345">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="346" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A346" s="2">
         <v>37081</v>
       </c>
@@ -47581,8 +48620,11 @@
       <c r="S346" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="347" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T346">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="347" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A347" s="2">
         <v>37081</v>
       </c>
@@ -47640,8 +48682,11 @@
       <c r="S347" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="348" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T347">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="348" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A348" s="2">
         <v>37081</v>
       </c>
@@ -47699,8 +48744,11 @@
       <c r="S348" t="s">
         <v>1578</v>
       </c>
-    </row>
-    <row r="349" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T348">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="349" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A349" s="2">
         <v>37081</v>
       </c>
@@ -47758,8 +48806,11 @@
       <c r="S349" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="350" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T349">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="350" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A350" s="2">
         <v>37081</v>
       </c>
@@ -47817,8 +48868,11 @@
       <c r="S350" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="351" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T350">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="351" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A351" s="2">
         <v>37081</v>
       </c>
@@ -47876,8 +48930,11 @@
       <c r="S351" t="s">
         <v>1576</v>
       </c>
-    </row>
-    <row r="352" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T351">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="352" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A352" s="2">
         <v>37081</v>
       </c>
@@ -47935,8 +48992,11 @@
       <c r="S352" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="353" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T352">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="353" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A353" s="2">
         <v>37081</v>
       </c>
@@ -47994,8 +49054,11 @@
       <c r="S353" t="s">
         <v>1576</v>
       </c>
-    </row>
-    <row r="354" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T353">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="354" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A354" s="2">
         <v>37081</v>
       </c>
@@ -48053,8 +49116,11 @@
       <c r="S354" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="355" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T354">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="355" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A355" s="2">
         <v>37081</v>
       </c>
@@ -48112,8 +49178,11 @@
       <c r="S355" t="s">
         <v>1579</v>
       </c>
-    </row>
-    <row r="356" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T355">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="356" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A356" s="2">
         <v>37151</v>
       </c>
@@ -48171,8 +49240,11 @@
       <c r="S356" t="s">
         <v>1576</v>
       </c>
-    </row>
-    <row r="357" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T356">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="357" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A357" s="2">
         <v>37151</v>
       </c>
@@ -48230,8 +49302,11 @@
       <c r="S357" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="358" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T357">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="358" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A358" s="2">
         <v>37151</v>
       </c>
@@ -48289,8 +49364,11 @@
       <c r="S358" t="s">
         <v>1576</v>
       </c>
-    </row>
-    <row r="359" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T358">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="359" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A359" s="2">
         <v>37151</v>
       </c>
@@ -48348,8 +49426,11 @@
       <c r="S359" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="360" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T359">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="360" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A360" s="2">
         <v>37151</v>
       </c>
@@ -48407,8 +49488,11 @@
       <c r="S360" t="s">
         <v>1576</v>
       </c>
-    </row>
-    <row r="361" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T360">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="361" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A361" s="2">
         <v>37151</v>
       </c>
@@ -48466,8 +49550,11 @@
       <c r="S361" t="s">
         <v>1576</v>
       </c>
-    </row>
-    <row r="362" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T361">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="362" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A362" s="2">
         <v>37151</v>
       </c>
@@ -48525,8 +49612,11 @@
       <c r="S362" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="363" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T362">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="363" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A363" s="2">
         <v>37151</v>
       </c>
@@ -48584,8 +49674,11 @@
       <c r="S363" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="364" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T363">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="364" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A364" s="2">
         <v>37151</v>
       </c>
@@ -48643,8 +49736,11 @@
       <c r="S364" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="365" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T364">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="365" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A365" s="2">
         <v>37151</v>
       </c>
@@ -48702,8 +49798,11 @@
       <c r="S365" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="366" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T365">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="366" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A366" s="2">
         <v>37151</v>
       </c>
@@ -48761,8 +49860,11 @@
       <c r="S366" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="367" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T366">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="367" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A367" s="2">
         <v>37151</v>
       </c>
@@ -48820,8 +49922,11 @@
       <c r="S367" t="s">
         <v>1578</v>
       </c>
-    </row>
-    <row r="368" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T367">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="368" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A368" s="2">
         <v>37151</v>
       </c>
@@ -48879,8 +49984,11 @@
       <c r="S368" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="369" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T368">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="369" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A369" s="2">
         <v>37151</v>
       </c>
@@ -48938,8 +50046,11 @@
       <c r="S369" t="s">
         <v>1578</v>
       </c>
-    </row>
-    <row r="370" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T369">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="370" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A370" s="2">
         <v>37151</v>
       </c>
@@ -48997,8 +50108,11 @@
       <c r="S370" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="371" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T370">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="371" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A371" s="2">
         <v>37151</v>
       </c>
@@ -49056,8 +50170,11 @@
       <c r="S371" t="s">
         <v>1579</v>
       </c>
-    </row>
-    <row r="372" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T371">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="372" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A372" s="2">
         <v>37151</v>
       </c>
@@ -49115,8 +50232,11 @@
       <c r="S372" t="s">
         <v>1578</v>
       </c>
-    </row>
-    <row r="373" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T372">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="373" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A373" s="2">
         <v>37151</v>
       </c>
@@ -49174,8 +50294,11 @@
       <c r="S373" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="374" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T373">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="374" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A374" s="2">
         <v>37151</v>
       </c>
@@ -49233,8 +50356,11 @@
       <c r="S374" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="375" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T374">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="375" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A375" s="2">
         <v>37151</v>
       </c>
@@ -49292,8 +50418,11 @@
       <c r="S375" t="s">
         <v>1578</v>
       </c>
-    </row>
-    <row r="376" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T375">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="376" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A376" s="2">
         <v>37151</v>
       </c>
@@ -49351,8 +50480,11 @@
       <c r="S376" t="s">
         <v>1576</v>
       </c>
-    </row>
-    <row r="377" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T376">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="377" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A377" s="2">
         <v>37151</v>
       </c>
@@ -49410,8 +50542,11 @@
       <c r="S377" t="s">
         <v>1579</v>
       </c>
-    </row>
-    <row r="378" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T377">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="378" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A378" s="2">
         <v>37151</v>
       </c>
@@ -49469,8 +50604,11 @@
       <c r="S378" t="s">
         <v>1578</v>
       </c>
-    </row>
-    <row r="379" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T378">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="379" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A379" s="2">
         <v>37151</v>
       </c>
@@ -49528,8 +50666,11 @@
       <c r="S379" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="380" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T379">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="380" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A380" s="2">
         <v>37151</v>
       </c>
@@ -49587,8 +50728,11 @@
       <c r="S380" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="381" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T380">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="381" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A381" s="2">
         <v>37151</v>
       </c>
@@ -49646,8 +50790,11 @@
       <c r="S381" t="s">
         <v>1579</v>
       </c>
-    </row>
-    <row r="382" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T381">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="382" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A382" s="2">
         <v>37151</v>
       </c>
@@ -49705,8 +50852,11 @@
       <c r="S382" t="s">
         <v>1576</v>
       </c>
-    </row>
-    <row r="383" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T382">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="383" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A383" s="2">
         <v>37151</v>
       </c>
@@ -49764,8 +50914,11 @@
       <c r="S383" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="384" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T383">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="384" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A384" s="2">
         <v>37151</v>
       </c>
@@ -49823,8 +50976,11 @@
       <c r="S384" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="385" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T384">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="385" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A385" s="2">
         <v>37151</v>
       </c>
@@ -49882,8 +51038,11 @@
       <c r="S385" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="386" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T385">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="386" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A386" s="2">
         <v>37151</v>
       </c>
@@ -49941,8 +51100,11 @@
       <c r="S386" t="s">
         <v>1579</v>
       </c>
-    </row>
-    <row r="387" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T386">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="387" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A387" s="2">
         <v>37151</v>
       </c>
@@ -50000,8 +51162,11 @@
       <c r="S387" t="s">
         <v>1578</v>
       </c>
-    </row>
-    <row r="388" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T387">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="388" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A388" s="2">
         <v>37151</v>
       </c>
@@ -50059,8 +51224,11 @@
       <c r="S388" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="389" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T388">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="389" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A389" s="2">
         <v>37151</v>
       </c>
@@ -50118,8 +51286,11 @@
       <c r="S389" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="390" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T389">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="390" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A390" s="2">
         <v>37157</v>
       </c>
@@ -50177,8 +51348,11 @@
       <c r="S390" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="391" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T390">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="391" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A391" s="2">
         <v>37157</v>
       </c>
@@ -50236,8 +51410,11 @@
       <c r="S391" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="392" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T391">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="392" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A392" s="2">
         <v>37157</v>
       </c>
@@ -50295,8 +51472,11 @@
       <c r="S392" t="s">
         <v>1576</v>
       </c>
-    </row>
-    <row r="393" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T392">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="393" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A393" s="2">
         <v>37157</v>
       </c>
@@ -50354,8 +51534,11 @@
       <c r="S393" t="s">
         <v>1576</v>
       </c>
-    </row>
-    <row r="394" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T393">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="394" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A394" s="2">
         <v>37157</v>
       </c>
@@ -50413,8 +51596,11 @@
       <c r="S394" t="s">
         <v>1576</v>
       </c>
-    </row>
-    <row r="395" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T394">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="395" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A395" s="2">
         <v>37157</v>
       </c>
@@ -50472,8 +51658,11 @@
       <c r="S395" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="396" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T395">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="396" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A396" s="2">
         <v>37157</v>
       </c>
@@ -50531,8 +51720,11 @@
       <c r="S396" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="397" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T396">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="397" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A397" s="2">
         <v>37157</v>
       </c>
@@ -50590,8 +51782,11 @@
       <c r="S397" t="s">
         <v>1578</v>
       </c>
-    </row>
-    <row r="398" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T397">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="398" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A398" s="2">
         <v>37157</v>
       </c>
@@ -50649,8 +51844,11 @@
       <c r="S398" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="399" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T398">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="399" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A399" s="2">
         <v>37157</v>
       </c>
@@ -50708,8 +51906,11 @@
       <c r="S399" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="400" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T399">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="400" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A400" s="2">
         <v>37157</v>
       </c>
@@ -50767,8 +51968,11 @@
       <c r="S400" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="401" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T400">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="401" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A401" s="2">
         <v>37157</v>
       </c>
@@ -50826,8 +52030,11 @@
       <c r="S401" t="s">
         <v>1576</v>
       </c>
-    </row>
-    <row r="402" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T401">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="402" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A402" s="2">
         <v>37157</v>
       </c>
@@ -50885,8 +52092,11 @@
       <c r="S402" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="403" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T402">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="403" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A403" s="2">
         <v>37157</v>
       </c>
@@ -50944,8 +52154,11 @@
       <c r="S403" t="s">
         <v>1578</v>
       </c>
-    </row>
-    <row r="404" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T403">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="404" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A404" s="2">
         <v>37157</v>
       </c>
@@ -51003,8 +52216,11 @@
       <c r="S404" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="405" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T404">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="405" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A405" s="2">
         <v>37157</v>
       </c>
@@ -51062,8 +52278,11 @@
       <c r="S405" t="s">
         <v>1576</v>
       </c>
-    </row>
-    <row r="406" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T405">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="406" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A406" s="2">
         <v>37157</v>
       </c>
@@ -51121,8 +52340,11 @@
       <c r="S406" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="407" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T406">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="407" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A407" s="2">
         <v>37157</v>
       </c>
@@ -51180,8 +52402,11 @@
       <c r="S407" t="s">
         <v>1576</v>
       </c>
-    </row>
-    <row r="408" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T407">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="408" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A408" s="2">
         <v>37157</v>
       </c>
@@ -51239,8 +52464,11 @@
       <c r="S408" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="409" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T408">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="409" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A409" s="2">
         <v>37157</v>
       </c>
@@ -51298,8 +52526,11 @@
       <c r="S409" t="s">
         <v>1576</v>
       </c>
-    </row>
-    <row r="410" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T409">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="410" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A410" s="2">
         <v>37157</v>
       </c>
@@ -51357,8 +52588,11 @@
       <c r="S410" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="411" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T410">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="411" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A411" s="2">
         <v>37157</v>
       </c>
@@ -51416,8 +52650,11 @@
       <c r="S411" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="412" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T411">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="412" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A412" s="2">
         <v>37169</v>
       </c>
@@ -51475,8 +52712,11 @@
       <c r="S412" t="s">
         <v>1579</v>
       </c>
-    </row>
-    <row r="413" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T412">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="413" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A413" s="2">
         <v>37169</v>
       </c>
@@ -51534,8 +52774,11 @@
       <c r="S413" t="s">
         <v>1579</v>
       </c>
-    </row>
-    <row r="414" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T413">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="414" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A414" s="2">
         <v>37169</v>
       </c>
@@ -51593,8 +52836,11 @@
       <c r="S414" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="415" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T414">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="415" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A415" s="2">
         <v>37169</v>
       </c>
@@ -51652,8 +52898,11 @@
       <c r="S415" t="s">
         <v>1576</v>
       </c>
-    </row>
-    <row r="416" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T415">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="416" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A416" s="2">
         <v>37169</v>
       </c>
@@ -51711,8 +52960,11 @@
       <c r="S416" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="417" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T416">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="417" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A417" s="2">
         <v>37169</v>
       </c>
@@ -51770,8 +53022,11 @@
       <c r="S417" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="418" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T417">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="418" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A418" s="2">
         <v>37169</v>
       </c>
@@ -51829,8 +53084,11 @@
       <c r="S418" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="419" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T418">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="419" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A419" s="2">
         <v>37169</v>
       </c>
@@ -51888,8 +53146,11 @@
       <c r="S419" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="420" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T419">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="420" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A420" s="2">
         <v>37169</v>
       </c>
@@ -51947,8 +53208,11 @@
       <c r="S420" t="s">
         <v>1576</v>
       </c>
-    </row>
-    <row r="421" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T420">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="421" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A421" s="2">
         <v>37169</v>
       </c>
@@ -52006,8 +53270,11 @@
       <c r="S421" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="422" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T421">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="422" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A422" s="2">
         <v>37169</v>
       </c>
@@ -52065,8 +53332,11 @@
       <c r="S422" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="423" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T422">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="423" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A423" s="2">
         <v>37169</v>
       </c>
@@ -52124,8 +53394,11 @@
       <c r="S423" t="s">
         <v>1576</v>
       </c>
-    </row>
-    <row r="424" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T423">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="424" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A424" s="2">
         <v>37169</v>
       </c>
@@ -52183,8 +53456,11 @@
       <c r="S424" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="425" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T424">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="425" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A425" s="2">
         <v>37171</v>
       </c>
@@ -52242,8 +53518,11 @@
       <c r="S425" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="426" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T425">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="426" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A426" s="2">
         <v>37171</v>
       </c>
@@ -52301,8 +53580,11 @@
       <c r="S426" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="427" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T426">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="427" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A427" s="2">
         <v>37171</v>
       </c>
@@ -52360,8 +53642,11 @@
       <c r="S427" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="428" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T427">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="428" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A428" s="2">
         <v>37171</v>
       </c>
@@ -52419,8 +53704,11 @@
       <c r="S428" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="429" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T428">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="429" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A429" s="2">
         <v>37171</v>
       </c>
@@ -52478,8 +53766,11 @@
       <c r="S429" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="430" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T429">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="430" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A430" s="2">
         <v>37171</v>
       </c>
@@ -52537,8 +53828,11 @@
       <c r="S430" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="431" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T430">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="431" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A431" s="2">
         <v>37171</v>
       </c>
@@ -52596,8 +53890,11 @@
       <c r="S431" t="s">
         <v>1576</v>
       </c>
-    </row>
-    <row r="432" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T431">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="432" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A432" s="2">
         <v>37171</v>
       </c>
@@ -52655,8 +53952,11 @@
       <c r="S432" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="433" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T432">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="433" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A433" s="2">
         <v>37171</v>
       </c>
@@ -52714,8 +54014,11 @@
       <c r="S433" t="s">
         <v>1576</v>
       </c>
-    </row>
-    <row r="434" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T433">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="434" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A434" s="2">
         <v>37171</v>
       </c>
@@ -52773,8 +54076,11 @@
       <c r="S434" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="435" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T434">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="435" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A435" s="2">
         <v>37171</v>
       </c>
@@ -52832,8 +54138,11 @@
       <c r="S435" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="436" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T435">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="436" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A436" s="2">
         <v>37171</v>
       </c>
@@ -52891,8 +54200,11 @@
       <c r="S436" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="437" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T436">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="437" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A437" s="2">
         <v>37171</v>
       </c>
@@ -52950,8 +54262,11 @@
       <c r="S437" t="s">
         <v>1578</v>
       </c>
-    </row>
-    <row r="438" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T437">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="438" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A438" s="2">
         <v>37171</v>
       </c>
@@ -53009,8 +54324,11 @@
       <c r="S438" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="439" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T438">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="439" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A439" s="2">
         <v>37171</v>
       </c>
@@ -53068,8 +54386,11 @@
       <c r="S439" t="s">
         <v>1576</v>
       </c>
-    </row>
-    <row r="440" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T439">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="440" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A440" s="2">
         <v>37171</v>
       </c>
@@ -53127,8 +54448,11 @@
       <c r="S440" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="441" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T440">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="441" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A441" s="2">
         <v>37171</v>
       </c>
@@ -53186,8 +54510,11 @@
       <c r="S441" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="442" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T441">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="442" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A442" s="2">
         <v>37171</v>
       </c>
@@ -53245,8 +54572,11 @@
       <c r="S442" t="s">
         <v>1576</v>
       </c>
-    </row>
-    <row r="443" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T442">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="443" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A443" s="2">
         <v>37171</v>
       </c>
@@ -53304,8 +54634,11 @@
       <c r="S443" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="444" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T443">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="444" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A444" s="2">
         <v>37171</v>
       </c>
@@ -53363,8 +54696,11 @@
       <c r="S444" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="445" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T444">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="445" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A445" s="2">
         <v>37171</v>
       </c>
@@ -53422,8 +54758,11 @@
       <c r="S445" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="446" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T445">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="446" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A446" s="2">
         <v>37171</v>
       </c>
@@ -53481,8 +54820,11 @@
       <c r="S446" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="447" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T446">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="447" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A447" s="2">
         <v>37171</v>
       </c>
@@ -53540,8 +54882,11 @@
       <c r="S447" t="s">
         <v>1576</v>
       </c>
-    </row>
-    <row r="448" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T447">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="448" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A448" s="2">
         <v>37189</v>
       </c>
@@ -53599,8 +54944,11 @@
       <c r="S448" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="449" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T448">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="449" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A449" s="2">
         <v>37189</v>
       </c>
@@ -53658,8 +55006,11 @@
       <c r="S449" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="450" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T449">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="450" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A450" s="2">
         <v>37189</v>
       </c>
@@ -53717,8 +55068,11 @@
       <c r="S450" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="451" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T450">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="451" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A451" s="2">
         <v>37189</v>
       </c>
@@ -53776,8 +55130,11 @@
       <c r="S451" t="s">
         <v>1576</v>
       </c>
-    </row>
-    <row r="452" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T451">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="452" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A452" s="2">
         <v>37189</v>
       </c>
@@ -53835,8 +55192,11 @@
       <c r="S452" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="453" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T452">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="453" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A453" s="2">
         <v>37189</v>
       </c>
@@ -53894,8 +55254,11 @@
       <c r="S453" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="454" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T453">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="454" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A454" s="2">
         <v>37189</v>
       </c>
@@ -53953,8 +55316,11 @@
       <c r="S454" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="455" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T454">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="455" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A455" s="2">
         <v>37189</v>
       </c>
@@ -54012,8 +55378,11 @@
       <c r="S455" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="456" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T455">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="456" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A456" s="2">
         <v>37189</v>
       </c>
@@ -54071,8 +55440,11 @@
       <c r="S456" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="457" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T456">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="457" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A457" s="2">
         <v>37189</v>
       </c>
@@ -54130,8 +55502,11 @@
       <c r="S457" t="s">
         <v>1576</v>
       </c>
-    </row>
-    <row r="458" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T457">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="458" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A458" s="2">
         <v>37189</v>
       </c>
@@ -54189,8 +55564,11 @@
       <c r="S458" t="s">
         <v>1576</v>
       </c>
-    </row>
-    <row r="459" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T458">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="459" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A459" s="2">
         <v>37189</v>
       </c>
@@ -54248,8 +55626,11 @@
       <c r="S459" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="460" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T459">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="460" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A460" s="2">
         <v>37189</v>
       </c>
@@ -54307,8 +55688,11 @@
       <c r="S460" t="s">
         <v>1579</v>
       </c>
-    </row>
-    <row r="461" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T460">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="461" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A461" s="2">
         <v>37193</v>
       </c>
@@ -54366,8 +55750,11 @@
       <c r="S461" t="s">
         <v>1576</v>
       </c>
-    </row>
-    <row r="462" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T461">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="462" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A462" s="2">
         <v>37193</v>
       </c>
@@ -54425,8 +55812,11 @@
       <c r="S462" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="463" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T462">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="463" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A463" s="2">
         <v>37193</v>
       </c>
@@ -54484,8 +55874,11 @@
       <c r="S463" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="464" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T463">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="464" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A464" s="2">
         <v>37193</v>
       </c>
@@ -54543,8 +55936,11 @@
       <c r="S464" t="s">
         <v>1576</v>
       </c>
-    </row>
-    <row r="465" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T464">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="465" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A465" s="2">
         <v>37193</v>
       </c>
@@ -54602,8 +55998,11 @@
       <c r="S465" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="466" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T465">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="466" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A466" s="2">
         <v>37193</v>
       </c>
@@ -54661,8 +56060,11 @@
       <c r="S466" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="467" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T466">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="467" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A467" s="2">
         <v>37193</v>
       </c>
@@ -54720,8 +56122,11 @@
       <c r="S467" t="s">
         <v>1576</v>
       </c>
-    </row>
-    <row r="468" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T467">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="468" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A468" s="2">
         <v>37193</v>
       </c>
@@ -54779,8 +56184,11 @@
       <c r="S468" t="s">
         <v>1576</v>
       </c>
-    </row>
-    <row r="469" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T468">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="469" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A469" s="2">
         <v>37193</v>
       </c>
@@ -54838,8 +56246,11 @@
       <c r="S469" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="470" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T469">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="470" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A470" s="2">
         <v>37193</v>
       </c>
@@ -54897,8 +56308,11 @@
       <c r="S470" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="471" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T470">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="471" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A471" s="2">
         <v>37193</v>
       </c>
@@ -54956,8 +56370,11 @@
       <c r="S471" t="s">
         <v>1576</v>
       </c>
-    </row>
-    <row r="472" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T471">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="472" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A472" s="2">
         <v>37193</v>
       </c>
@@ -55015,8 +56432,11 @@
       <c r="S472" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="473" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T472">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="473" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A473" s="2">
         <v>37193</v>
       </c>
@@ -55074,8 +56494,11 @@
       <c r="S473" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="474" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T473">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="474" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A474" s="2">
         <v>37193</v>
       </c>
@@ -55133,8 +56556,11 @@
       <c r="S474" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="475" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T474">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="475" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A475" s="2">
         <v>37193</v>
       </c>
@@ -55192,8 +56618,11 @@
       <c r="S475" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="476" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T475">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="476" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A476" s="2">
         <v>37193</v>
       </c>
@@ -55251,8 +56680,11 @@
       <c r="S476" t="s">
         <v>1576</v>
       </c>
-    </row>
-    <row r="477" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T476">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="477" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A477" s="2">
         <v>37193</v>
       </c>
@@ -55310,8 +56742,11 @@
       <c r="S477" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="478" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T477">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="478" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A478" s="2">
         <v>37193</v>
       </c>
@@ -55369,8 +56804,11 @@
       <c r="S478" t="s">
         <v>1576</v>
       </c>
-    </row>
-    <row r="479" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T478">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="479" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A479" s="2">
         <v>37197</v>
       </c>
@@ -55428,8 +56866,11 @@
       <c r="S479" t="s">
         <v>1576</v>
       </c>
-    </row>
-    <row r="480" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T479">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="480" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A480" s="2">
         <v>37197</v>
       </c>
@@ -55487,8 +56928,11 @@
       <c r="S480" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="481" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T480">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="481" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A481" s="2">
         <v>37197</v>
       </c>
@@ -55546,8 +56990,11 @@
       <c r="S481" t="s">
         <v>1576</v>
       </c>
-    </row>
-    <row r="482" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T481">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="482" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A482" s="2">
         <v>37197</v>
       </c>
@@ -55605,8 +57052,11 @@
       <c r="S482" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="483" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T482">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="483" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A483" s="2">
         <v>37197</v>
       </c>
@@ -55664,8 +57114,11 @@
       <c r="S483" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="484" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T483">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="484" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A484" s="2">
         <v>37197</v>
       </c>
@@ -55723,8 +57176,11 @@
       <c r="S484" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="485" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T484">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="485" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A485" s="2">
         <v>37197</v>
       </c>
@@ -55782,8 +57238,11 @@
       <c r="S485" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="486" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T485">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="486" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A486" s="2">
         <v>37197</v>
       </c>
@@ -55841,8 +57300,11 @@
       <c r="S486" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="487" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T486">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="487" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A487" s="2">
         <v>37197</v>
       </c>
@@ -55900,8 +57362,11 @@
       <c r="S487" t="s">
         <v>1576</v>
       </c>
-    </row>
-    <row r="488" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T487">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="488" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A488" s="2">
         <v>37097</v>
       </c>
@@ -55959,8 +57424,11 @@
       <c r="S488" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="489" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T488">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="489" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A489" s="2">
         <v>37097</v>
       </c>
@@ -56018,8 +57486,11 @@
       <c r="S489" t="s">
         <v>1576</v>
       </c>
-    </row>
-    <row r="490" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T489">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="490" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A490" s="2">
         <v>37097</v>
       </c>
@@ -56077,8 +57548,11 @@
       <c r="S490" t="s">
         <v>1576</v>
       </c>
-    </row>
-    <row r="491" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T490">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="491" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A491" s="2">
         <v>37097</v>
       </c>
@@ -56136,8 +57610,11 @@
       <c r="S491" t="s">
         <v>1576</v>
       </c>
-    </row>
-    <row r="492" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T491">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="492" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A492" s="2">
         <v>37097</v>
       </c>
@@ -56195,8 +57672,11 @@
       <c r="S492" t="s">
         <v>1576</v>
       </c>
-    </row>
-    <row r="493" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T492">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="493" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A493" s="2">
         <v>37097</v>
       </c>
@@ -56254,8 +57734,11 @@
       <c r="S493" t="s">
         <v>1576</v>
       </c>
-    </row>
-    <row r="494" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T493">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="494" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A494" s="2">
         <v>37097</v>
       </c>
@@ -56313,8 +57796,11 @@
       <c r="S494" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="495" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T494">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="495" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A495" s="2">
         <v>37097</v>
       </c>
@@ -56372,8 +57858,11 @@
       <c r="S495" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="496" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T495">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="496" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A496" s="2">
         <v>37097</v>
       </c>
@@ -56431,8 +57920,11 @@
       <c r="S496" t="s">
         <v>1578</v>
       </c>
-    </row>
-    <row r="497" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T496">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="497" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A497" s="2">
         <v>37097</v>
       </c>
@@ -56490,8 +57982,11 @@
       <c r="S497" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="498" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T497">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="498" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A498" s="2">
         <v>37097</v>
       </c>
@@ -56549,8 +58044,11 @@
       <c r="S498" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="499" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T498">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="499" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A499" s="2">
         <v>37097</v>
       </c>
@@ -56608,8 +58106,11 @@
       <c r="S499" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="500" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T499">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="500" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A500" s="2">
         <v>37097</v>
       </c>
@@ -56667,8 +58168,11 @@
       <c r="S500" t="s">
         <v>1576</v>
       </c>
-    </row>
-    <row r="501" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T500">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="501" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A501" s="2">
         <v>37097</v>
       </c>
@@ -56726,8 +58230,11 @@
       <c r="S501" t="s">
         <v>1576</v>
       </c>
-    </row>
-    <row r="502" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T501">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="502" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A502" s="2">
         <v>37097</v>
       </c>
@@ -56785,8 +58292,11 @@
       <c r="S502" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="503" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T502">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="503" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A503" s="2">
         <v>37097</v>
       </c>
@@ -56844,8 +58354,11 @@
       <c r="S503" t="s">
         <v>1576</v>
       </c>
-    </row>
-    <row r="504" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T503">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="504" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A504" s="2">
         <v>37097</v>
       </c>
@@ -56903,8 +58416,11 @@
       <c r="S504" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="505" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T504">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="505" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A505" s="2">
         <v>37097</v>
       </c>
@@ -56962,8 +58478,11 @@
       <c r="S505" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="506" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T505">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="506" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A506" s="2">
         <v>37097</v>
       </c>
@@ -57021,8 +58540,11 @@
       <c r="S506" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="507" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T506">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="507" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A507" s="2">
         <v>37097</v>
       </c>
@@ -57080,8 +58602,11 @@
       <c r="S507" t="s">
         <v>1576</v>
       </c>
-    </row>
-    <row r="508" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T507">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="508" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A508" s="2">
         <v>37097</v>
       </c>
@@ -57139,8 +58664,11 @@
       <c r="S508" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="509" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T508">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="509" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A509" s="2">
         <v>37097</v>
       </c>
@@ -57198,8 +58726,11 @@
       <c r="S509" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="510" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T509">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="510" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A510" s="2">
         <v>37097</v>
       </c>
@@ -57257,8 +58788,11 @@
       <c r="S510" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="511" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T510">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="511" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A511" s="2">
         <v>37097</v>
       </c>
@@ -57316,8 +58850,11 @@
       <c r="S511" t="s">
         <v>1579</v>
       </c>
-    </row>
-    <row r="512" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T511">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="512" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A512" s="2">
         <v>37097</v>
       </c>
@@ -57375,8 +58912,11 @@
       <c r="S512" t="s">
         <v>1579</v>
       </c>
-    </row>
-    <row r="513" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T512">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="513" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A513" s="2">
         <v>37097</v>
       </c>
@@ -57434,8 +58974,11 @@
       <c r="S513" t="s">
         <v>1579</v>
       </c>
-    </row>
-    <row r="514" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T513">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="514" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A514" s="2">
         <v>37097</v>
       </c>
@@ -57493,8 +59036,11 @@
       <c r="S514" t="s">
         <v>1579</v>
       </c>
-    </row>
-    <row r="515" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T514">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="515" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A515" s="2">
         <v>37097</v>
       </c>
@@ -57552,8 +59098,11 @@
       <c r="S515" t="s">
         <v>1577</v>
       </c>
-    </row>
-    <row r="516" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T515">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="516" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A516" s="2">
         <v>37097</v>
       </c>
@@ -57611,8 +59160,11 @@
       <c r="S516" t="s">
         <v>1579</v>
       </c>
-    </row>
-    <row r="517" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T516">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="517" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A517" s="2">
         <v>37097</v>
       </c>
@@ -57670,8 +59222,11 @@
       <c r="S517" t="s">
         <v>1579</v>
       </c>
-    </row>
-    <row r="518" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T517">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="518" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A518" s="2">
         <v>37097</v>
       </c>
@@ -57729,8 +59284,11 @@
       <c r="S518" t="s">
         <v>1579</v>
       </c>
-    </row>
-    <row r="519" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T518">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="519" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A519" s="2">
         <v>37097</v>
       </c>
@@ -57788,8 +59346,11 @@
       <c r="S519" t="s">
         <v>1579</v>
       </c>
-    </row>
-    <row r="520" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T519">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="520" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A520" s="2">
         <v>37097</v>
       </c>
@@ -57847,8 +59408,11 @@
       <c r="S520" t="s">
         <v>1579</v>
       </c>
-    </row>
-    <row r="521" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T520">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="521" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A521" s="2">
         <v>37097</v>
       </c>
@@ -57906,8 +59470,11 @@
       <c r="S521" t="s">
         <v>1579</v>
       </c>
-    </row>
-    <row r="522" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T521">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="522" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A522" s="2">
         <v>37097</v>
       </c>
@@ -57965,8 +59532,11 @@
       <c r="S522" t="s">
         <v>1579</v>
       </c>
-    </row>
-    <row r="523" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T522">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="523" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A523" s="2">
         <v>37097</v>
       </c>
@@ -58024,8 +59594,11 @@
       <c r="S523" t="s">
         <v>1579</v>
       </c>
-    </row>
-    <row r="524" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T523">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="524" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A524" s="2">
         <v>37097</v>
       </c>
@@ -58083,8 +59656,11 @@
       <c r="S524" t="s">
         <v>1579</v>
       </c>
-    </row>
-    <row r="525" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T524">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="525" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A525" s="2">
         <v>37097</v>
       </c>
@@ -58142,8 +59718,11 @@
       <c r="S525" t="s">
         <v>1579</v>
       </c>
-    </row>
-    <row r="526" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T525">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="526" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A526" s="2">
         <v>37097</v>
       </c>
@@ -58201,8 +59780,11 @@
       <c r="S526" t="s">
         <v>1579</v>
       </c>
-    </row>
-    <row r="527" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T526">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="527" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A527" s="2">
         <v>37097</v>
       </c>
@@ -58260,8 +59842,11 @@
       <c r="S527" t="s">
         <v>1578</v>
       </c>
-    </row>
-    <row r="528" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T527">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="528" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A528" s="2">
         <v>37097</v>
       </c>
@@ -58319,8 +59904,11 @@
       <c r="S528" t="s">
         <v>1579</v>
       </c>
-    </row>
-    <row r="529" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T528">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="529" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A529" s="2">
         <v>37097</v>
       </c>
@@ -58378,8 +59966,11 @@
       <c r="S529" t="s">
         <v>1579</v>
       </c>
-    </row>
-    <row r="530" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T529">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="530" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A530" s="2">
         <v>37097</v>
       </c>
@@ -58437,8 +60028,11 @@
       <c r="S530" t="s">
         <v>1578</v>
       </c>
-    </row>
-    <row r="531" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T530">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="531" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A531" s="2">
         <v>37097</v>
       </c>
@@ -58496,8 +60090,11 @@
       <c r="S531" t="s">
         <v>1579</v>
       </c>
-    </row>
-    <row r="532" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T531">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="532" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A532" s="2">
         <v>37097</v>
       </c>
@@ -58555,8 +60152,11 @@
       <c r="S532" t="s">
         <v>1579</v>
       </c>
-    </row>
-    <row r="533" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T532">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="533" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A533" s="2">
         <v>37097</v>
       </c>
@@ -58614,9 +60214,18 @@
       <c r="S533" t="s">
         <v>1579</v>
       </c>
+      <c r="T533">
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:S533" xr:uid="{A7F1BB22-D0D6-4DBD-A1C6-B20ABF137412}"/>
+  <autoFilter ref="A1:T533" xr:uid="{A7F1BB22-D0D6-4DBD-A1C6-B20ABF137412}">
+    <filterColumn colId="19">
+      <filters>
+        <filter val="0"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <conditionalFormatting sqref="K2:K533">
     <cfRule type="cellIs" dxfId="2" priority="1" operator="greaterThan">
       <formula>0.5</formula>

--- a/SNAP_Bivariate_Classification_Dataset.xlsx
+++ b/SNAP_Bivariate_Classification_Dataset.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nowsh\Downloads\Research\Fall 2025\food_insecurity_dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{518BC16B-84BB-4E5C-82B1-DDBCD822611F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{119A3609-4A34-45D4-A249-25A5140D7D70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="1" xr2:uid="{85984DDD-8E03-4E71-BB7D-ACE5956AC118}"/>
   </bookViews>
@@ -27161,7 +27161,6 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A7F1BB22-D0D6-4DBD-A1C6-B20ABF137412}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:T533"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -58792,7 +58791,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="511" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+    <row r="511" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A511" s="2">
         <v>37097</v>
       </c>
@@ -58854,7 +58853,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="512" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+    <row r="512" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A512" s="2">
         <v>37097</v>
       </c>
@@ -58916,7 +58915,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="513" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+    <row r="513" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A513" s="2">
         <v>37097</v>
       </c>
@@ -59102,7 +59101,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="516" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+    <row r="516" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A516" s="2">
         <v>37097</v>
       </c>
@@ -59164,7 +59163,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="517" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+    <row r="517" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A517" s="2">
         <v>37097</v>
       </c>
@@ -59226,7 +59225,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="518" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+    <row r="518" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A518" s="2">
         <v>37097</v>
       </c>
@@ -59288,7 +59287,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="519" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+    <row r="519" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A519" s="2">
         <v>37097</v>
       </c>
@@ -59350,7 +59349,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="520" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+    <row r="520" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A520" s="2">
         <v>37097</v>
       </c>
@@ -59412,7 +59411,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="521" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+    <row r="521" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A521" s="2">
         <v>37097</v>
       </c>
@@ -59474,7 +59473,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="522" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+    <row r="522" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A522" s="2">
         <v>37097</v>
       </c>
@@ -59536,7 +59535,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="523" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+    <row r="523" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A523" s="2">
         <v>37097</v>
       </c>
@@ -59598,7 +59597,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="524" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+    <row r="524" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A524" s="2">
         <v>37097</v>
       </c>
@@ -59660,7 +59659,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="525" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+    <row r="525" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A525" s="2">
         <v>37097</v>
       </c>
@@ -59722,7 +59721,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="526" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+    <row r="526" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A526" s="2">
         <v>37097</v>
       </c>
@@ -59784,7 +59783,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="527" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+    <row r="527" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A527" s="2">
         <v>37097</v>
       </c>
@@ -59846,7 +59845,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="528" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+    <row r="528" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A528" s="2">
         <v>37097</v>
       </c>
@@ -59908,7 +59907,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="529" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+    <row r="529" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A529" s="2">
         <v>37097</v>
       </c>
@@ -59970,7 +59969,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="530" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+    <row r="530" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A530" s="2">
         <v>37097</v>
       </c>
@@ -60032,7 +60031,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="531" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+    <row r="531" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A531" s="2">
         <v>37097</v>
       </c>
@@ -60094,7 +60093,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="532" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+    <row r="532" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A532" s="2">
         <v>37097</v>
       </c>
@@ -60156,7 +60155,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="533" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
+    <row r="533" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A533" s="2">
         <v>37097</v>
       </c>
@@ -60219,13 +60218,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:T533" xr:uid="{A7F1BB22-D0D6-4DBD-A1C6-B20ABF137412}">
-    <filterColumn colId="19">
-      <filters>
-        <filter val="0"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:T533" xr:uid="{A7F1BB22-D0D6-4DBD-A1C6-B20ABF137412}"/>
   <conditionalFormatting sqref="K2:K533">
     <cfRule type="cellIs" dxfId="2" priority="1" operator="greaterThan">
       <formula>0.5</formula>

--- a/SNAP_Bivariate_Classification_Dataset.xlsx
+++ b/SNAP_Bivariate_Classification_Dataset.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nowsh\Downloads\Research\Fall 2025\food_insecurity_dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{119A3609-4A34-45D4-A249-25A5140D7D70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EDA4F91-6BD1-4726-A542-7F8045FA6D4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="1" xr2:uid="{85984DDD-8E03-4E71-BB7D-ACE5956AC118}"/>
   </bookViews>
@@ -4879,7 +4879,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4889,6 +4889,10 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -27164,72 +27168,84 @@
   <dimension ref="A1:T533"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="10.81640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.7265625" customWidth="1"/>
-    <col min="8" max="8" width="10.1796875" customWidth="1"/>
-    <col min="15" max="15" width="35.1796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="5.90625" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="10.81640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.81640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.54296875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="25.26953125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="22.453125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="21.6328125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.81640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.81640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="31.7265625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="10.26953125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="34.36328125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="22.453125" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="34.36328125" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="16.7265625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="25.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" ht="52.5" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
+    <row r="1" spans="1:20" s="6" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="5" t="s">
         <v>1568</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="5" t="s">
         <v>1569</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="5" t="s">
         <v>1564</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="5" t="s">
         <v>1580</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="N1" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="O1" s="5" t="s">
         <v>1565</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="P1" s="5" t="s">
         <v>1566</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="Q1" s="5" t="s">
         <v>1567</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="R1" s="5" t="s">
         <v>1574</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="S1" s="5" t="s">
         <v>1575</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="T1" s="5" t="s">
         <v>1581</v>
       </c>
     </row>
